--- a/LME/parser/lme/data/LME_db_new.xlsx
+++ b/LME/parser/lme/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1182"/>
+  <dimension ref="A1:G1183"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -27585,6 +27585,29 @@
         <v>54725</v>
       </c>
     </row>
+    <row r="1183" spans="1:7">
+      <c r="A1183" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B1183">
+        <v>3255.5</v>
+      </c>
+      <c r="C1183">
+        <v>14355</v>
+      </c>
+      <c r="D1183">
+        <v>1873</v>
+      </c>
+      <c r="E1183">
+        <v>16530</v>
+      </c>
+      <c r="F1183">
+        <v>4000</v>
+      </c>
+      <c r="G1183">
+        <v>53950</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/lme/data/LME_db_new.xlsx
+++ b/LME/parser/lme/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1183"/>
+  <dimension ref="A1:G1184"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -27608,6 +27608,11 @@
         <v>53950</v>
       </c>
     </row>
+    <row r="1184" spans="1:7">
+      <c r="A1184" s="2">
+        <v>46268</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/lme/data/LME_db_new.xlsx
+++ b/LME/parser/lme/data/LME_db_new.xlsx
@@ -27612,6 +27612,24 @@
       <c r="A1184" s="2">
         <v>46268</v>
       </c>
+      <c r="B1184">
+        <v>3303</v>
+      </c>
+      <c r="C1184">
+        <v>14359</v>
+      </c>
+      <c r="D1184">
+        <v>1870</v>
+      </c>
+      <c r="E1184">
+        <v>16615</v>
+      </c>
+      <c r="F1184">
+        <v>3995.5</v>
+      </c>
+      <c r="G1184">
+        <v>54450</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/LME/parser/lme/data/LME_db_new.xlsx
+++ b/LME/parser/lme/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1184"/>
+  <dimension ref="A1:G1185"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -27631,6 +27631,29 @@
         <v>54450</v>
       </c>
     </row>
+    <row r="1185" spans="1:7">
+      <c r="A1185" s="2">
+        <v>46269</v>
+      </c>
+      <c r="B1185">
+        <v>3292.5</v>
+      </c>
+      <c r="C1185">
+        <v>14371</v>
+      </c>
+      <c r="D1185">
+        <v>1871</v>
+      </c>
+      <c r="E1185">
+        <v>16690</v>
+      </c>
+      <c r="F1185">
+        <v>4087</v>
+      </c>
+      <c r="G1185">
+        <v>54525</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/lme/data/LME_db_new.xlsx
+++ b/LME/parser/lme/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1185"/>
+  <dimension ref="A1:G1186"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -27654,6 +27654,29 @@
         <v>54525</v>
       </c>
     </row>
+    <row r="1186" spans="1:7">
+      <c r="A1186" s="2">
+        <v>46272</v>
+      </c>
+      <c r="B1186">
+        <v>3310</v>
+      </c>
+      <c r="C1186">
+        <v>14540</v>
+      </c>
+      <c r="D1186">
+        <v>1875</v>
+      </c>
+      <c r="E1186">
+        <v>16600</v>
+      </c>
+      <c r="F1186">
+        <v>4157</v>
+      </c>
+      <c r="G1186">
+        <v>55100</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/lme/data/LME_db_new.xlsx
+++ b/LME/parser/lme/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1186"/>
+  <dimension ref="A1:G1187"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -27677,6 +27677,29 @@
         <v>55100</v>
       </c>
     </row>
+    <row r="1187" spans="1:7">
+      <c r="A1187" s="2">
+        <v>46273</v>
+      </c>
+      <c r="B1187">
+        <v>3325</v>
+      </c>
+      <c r="C1187">
+        <v>14737</v>
+      </c>
+      <c r="D1187">
+        <v>1859</v>
+      </c>
+      <c r="E1187">
+        <v>16675</v>
+      </c>
+      <c r="F1187">
+        <v>4110</v>
+      </c>
+      <c r="G1187">
+        <v>54900</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/lme/data/LME_db_new.xlsx
+++ b/LME/parser/lme/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1187"/>
+  <dimension ref="A1:G1188"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -27700,6 +27700,29 @@
         <v>54900</v>
       </c>
     </row>
+    <row r="1188" spans="1:7">
+      <c r="A1188" s="2">
+        <v>46274</v>
+      </c>
+      <c r="B1188">
+        <v>3352</v>
+      </c>
+      <c r="C1188">
+        <v>14672</v>
+      </c>
+      <c r="D1188">
+        <v>1871</v>
+      </c>
+      <c r="E1188">
+        <v>16675</v>
+      </c>
+      <c r="F1188">
+        <v>4186</v>
+      </c>
+      <c r="G1188">
+        <v>55000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/lme/data/LME_db_new.xlsx
+++ b/LME/parser/lme/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1188"/>
+  <dimension ref="A1:G1189"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -27723,6 +27723,29 @@
         <v>55000</v>
       </c>
     </row>
+    <row r="1189" spans="1:7">
+      <c r="A1189" s="2">
+        <v>46275</v>
+      </c>
+      <c r="B1189">
+        <v>3343</v>
+      </c>
+      <c r="C1189">
+        <v>14390</v>
+      </c>
+      <c r="D1189">
+        <v>1870.5</v>
+      </c>
+      <c r="E1189">
+        <v>16630</v>
+      </c>
+      <c r="F1189">
+        <v>4105</v>
+      </c>
+      <c r="G1189">
+        <v>54750</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/lme/data/LME_db_new.xlsx
+++ b/LME/parser/lme/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1189"/>
+  <dimension ref="A1:G1190"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -27746,6 +27746,29 @@
         <v>54750</v>
       </c>
     </row>
+    <row r="1190" spans="1:7">
+      <c r="A1190" s="2">
+        <v>46276</v>
+      </c>
+      <c r="B1190">
+        <v>3274</v>
+      </c>
+      <c r="C1190">
+        <v>14238.5</v>
+      </c>
+      <c r="D1190">
+        <v>1854</v>
+      </c>
+      <c r="E1190">
+        <v>16270</v>
+      </c>
+      <c r="F1190">
+        <v>4015</v>
+      </c>
+      <c r="G1190">
+        <v>53755</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
